--- a/人员信息填写模板.xlsx
+++ b/人员信息填写模板.xlsx
@@ -695,7 +695,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -777,6 +777,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0"/>
@@ -904,6 +916,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>填表说明</author>
+    <author>模板</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -966,10 +979,10 @@
       <text>
         <t>【层级】★建议
 分类：核心信息
-决定框的颜色和在图上的位置，从下拉里选，共 13 档（由高到低）：
-总经理／副总经理／中心总监／中心副总监／部门总监／部门副总监／
-部门经理／部门副经理／主管／组长／核心骨干／基石员工／流动培养
-正职副职各占一档。留空则按「岗位」推断，认不出按「基石员工」处理。
+决定框的颜色和在图上的位置，从下拉里选，共 14 档（由高到低，括号里是「层级编号」）：
+总经理(1)／副总经理(2)／执行副总(3)／中心总监(4)／中心副总监(5)／部门总监(6)／部门副总监(7)／
+部门经理(8)／部门副经理(9)／主管(10)／组长(11)／核心骨干(12)／基石员工(13)／流动培养(14)
+正职副职各占一档。也可以不选文字，在「层级编号」列填括号里的数字，编号优先。留空则按「岗位」推断，认不出按「基石员工」处理。
 例：部门副经理</t>
       </text>
     </comment>
@@ -1136,6 +1149,16 @@
         <t>【显示顺序】可选
 分类：版式微调（一般不用填）
 数字，控制分组和人员先后，优先级最高于自动排序。</t>
+      </text>
+    </comment>
+    <comment ref="AN1" authorId="1" shapeId="0">
+      <text>
+        <t>【层级编号】选填
+分类：核心信息
+填 1～14 的数字，直接指定层级（见「←填写须知」层级表的编号列）：
+1 总经理、2 副总经理、3 执行副总、4 中心总监、5 中心副总监、6 部门总监、7 部门副总监、8 部门经理、9 部门副经理、10 主管、11 组长、12 核心骨干、13 基石员工、14 流动培养
+填了就以它为准，「层级」「岗位」的文字不再参与判定；留空则照旧按「层级」列。
+例：9（部门副经理）</t>
       </text>
     </comment>
   </commentList>
@@ -1360,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1000"/>
+  <dimension ref="A1:AN1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.79999923706055"/>
   <cols>
     <col width="13.79807662963867" customWidth="1" min="1" max="5"/>
@@ -1381,6 +1404,7 @@
     <col width="16" customWidth="1" min="27" max="27"/>
     <col width="13.79807662963867" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1577,6 +1601,11 @@
       <c r="AM1" s="27" t="inlineStr">
         <is>
           <t>显示顺序</t>
+        </is>
+      </c>
+      <c r="AN1" s="35" t="inlineStr">
+        <is>
+          <t>层级编号</t>
         </is>
       </c>
     </row>
@@ -1663,6 +1692,9 @@
       <c r="AK2" s="30" t="inlineStr"/>
       <c r="AL2" s="30" t="inlineStr"/>
       <c r="AM2" s="30" t="inlineStr"/>
+      <c r="AN2" s="36" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
@@ -1759,6 +1791,9 @@
       <c r="AK3" s="30" t="inlineStr"/>
       <c r="AL3" s="30" t="inlineStr"/>
       <c r="AM3" s="30" t="inlineStr"/>
+      <c r="AN3" s="36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="28" t="inlineStr">
@@ -1843,6 +1878,9 @@
       <c r="AK4" s="30" t="inlineStr"/>
       <c r="AL4" s="30" t="inlineStr"/>
       <c r="AM4" s="30" t="inlineStr"/>
+      <c r="AN4" s="36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
@@ -1935,6 +1973,9 @@
       <c r="AK5" s="30" t="inlineStr"/>
       <c r="AL5" s="30" t="inlineStr"/>
       <c r="AM5" s="30" t="inlineStr"/>
+      <c r="AN5" s="36" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
@@ -2023,6 +2064,9 @@
       <c r="AK6" s="30" t="inlineStr"/>
       <c r="AL6" s="30" t="inlineStr"/>
       <c r="AM6" s="30" t="inlineStr"/>
+      <c r="AN6" s="36" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
@@ -2119,6 +2163,9 @@
       <c r="AK7" s="30" t="inlineStr"/>
       <c r="AL7" s="30" t="inlineStr"/>
       <c r="AM7" s="30" t="inlineStr"/>
+      <c r="AN7" s="36" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
@@ -2207,6 +2254,9 @@
       <c r="AK8" s="30" t="inlineStr"/>
       <c r="AL8" s="30" t="inlineStr"/>
       <c r="AM8" s="30" t="inlineStr"/>
+      <c r="AN8" s="36" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
@@ -2299,6 +2349,9 @@
       <c r="AK9" s="30" t="inlineStr"/>
       <c r="AL9" s="30" t="inlineStr"/>
       <c r="AM9" s="30" t="inlineStr"/>
+      <c r="AN9" s="36" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="inlineStr">
@@ -2387,6 +2440,9 @@
       <c r="AK10" s="30" t="inlineStr"/>
       <c r="AL10" s="30" t="inlineStr"/>
       <c r="AM10" s="30" t="inlineStr"/>
+      <c r="AN10" s="36" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="28" t="inlineStr">
@@ -2479,6 +2535,9 @@
       <c r="AK11" s="30" t="inlineStr"/>
       <c r="AL11" s="30" t="inlineStr"/>
       <c r="AM11" s="30" t="inlineStr"/>
+      <c r="AN11" s="36" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="12">
       <c r="X12" s="34" t="n"/>
@@ -6437,7 +6496,7 @@
       <c r="Y1000" s="34" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在允许范围" error="请从下拉里选一个" type="list">
       <formula1>"总经理,副总经理,执行副总,中心总监,中心副总监,部门总监,部门副总监,部门经理,部门副经理,主管,组长,核心骨干,基石员工,流动培养"</formula1>
     </dataValidation>
@@ -6468,6 +6527,10 @@
     <dataValidation sqref="AL2:AL500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在允许范围" error="请从下拉里选一个" type="list">
       <formula1>"是"</formula1>
     </dataValidation>
+    <dataValidation sqref="AN2:AN500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="层级编号" error="请填 1～14 的整数（对照「←填写须知」的层级表）" type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>14</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -6497,6 +6560,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -6509,6 +6573,7 @@
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="4" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5" ht="19.20000076293945" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -6528,6 +6593,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="4" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -6673,6 +6739,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="4" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="19.20000076293945" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -6680,18 +6747,20 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>总经理 ＞ 副总经理 ＞ 执行副总 ＞ 中心总监 ＞ 中心副总监 ＞ 部门总监 ＞ 部门副总监 ＞ 部门经理 ＞ 部门副经理 ＞ 主管 ＞ 组长 ＞ 核心骨干 ＞ 基石员工 ＞ 流动培养
 副职单独成档，排在对应正职的下一级（框色更浅）；正副的具体差距再由「职等职级」列表达。
-「事业部总经理」属中心总监档，不是一把手。层级留空会按「岗位」自动推断。</t>
+「事业部总经理」属中心总监档，不是一把手。层级留空会按「岗位」自动推断。
+也可以在「人员名单」的「层级编号」列直接填下表的编号（1～14），填了就以编号为准，不再按文字推断。</t>
         </is>
       </c>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="4" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -6708,6 +6777,11 @@
           <t>在图上的位置</t>
         </is>
       </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -6725,6 +6799,9 @@
           <t>顶层框</t>
         </is>
       </c>
+      <c r="D20" s="38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -6742,6 +6819,9 @@
           <t>顶层框（与总经理并排）</t>
         </is>
       </c>
+      <c r="D21" s="38" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -6759,6 +6839,9 @@
           <t>顶层框下方（比副总经理低一档，单独占一行）</t>
         </is>
       </c>
+      <c r="D22" s="38" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -6776,6 +6859,9 @@
           <t>中心横条下方</t>
         </is>
       </c>
+      <c r="D23" s="38" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -6793,6 +6879,9 @@
           <t>中心横条下方</t>
         </is>
       </c>
+      <c r="D24" s="38" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -6810,6 +6899,9 @@
           <t>部门横条下方</t>
         </is>
       </c>
+      <c r="D25" s="38" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -6827,6 +6919,9 @@
           <t>部门横条下方</t>
         </is>
       </c>
+      <c r="D26" s="38" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -6844,6 +6939,9 @@
           <t>部门横条下方</t>
         </is>
       </c>
+      <c r="D27" s="38" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -6861,6 +6959,9 @@
           <t>部门横条下方</t>
         </is>
       </c>
+      <c r="D28" s="38" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -6878,6 +6979,9 @@
           <t>组头或组员</t>
         </is>
       </c>
+      <c r="D29" s="38" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -6895,6 +6999,9 @@
           <t>组头</t>
         </is>
       </c>
+      <c r="D30" s="38" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -6908,6 +7015,9 @@
           <t>组员</t>
         </is>
       </c>
+      <c r="D31" s="38" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
@@ -6925,6 +7035,9 @@
           <t>组员</t>
         </is>
       </c>
+      <c r="D32" s="38" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -6941,6 +7054,9 @@
         <is>
           <t>组员</t>
         </is>
+      </c>
+      <c r="D33" s="38" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="34" ht="19.20000076293945" customHeight="1"/>
@@ -7130,7 +7246,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
           <t>层级</t>
@@ -7144,7 +7260,8 @@
       <c r="C47" s="13" t="inlineStr">
         <is>
           <t>决定框的颜色和在图上的位置，从下拉里选。
-留空则按「岗位」推断，认不出按「基石员工」处理。</t>
+留空则按「岗位」推断，认不出按「基石员工」处理。
+也可以不选文字，改在「层级编号」列填 1～14 的数字（见上方层级表的编号列），编号优先。</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -7529,6 +7646,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr"/>
     </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
@@ -7597,6 +7715,7 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="21" t="inlineStr">
         <is>

--- a/人员信息填写模板.xlsx
+++ b/人员信息填写模板.xlsx
@@ -6518,9 +6518,6 @@
     <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在允许范围" error="请从下拉里选一个" type="list">
       <formula1>"本科,大专,中专,高中"</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在允许范围" error="请从下拉里选一个" type="list">
-      <formula1>"总经理,副总经理,执行副总,中心总监,中心副总监,部门总监,部门副总监,部门经理,部门副经理,主管,组长,核心骨干,基石员工,流动培养"</formula1>
-    </dataValidation>
     <dataValidation sqref="AK2:AK500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在允许范围" error="请从下拉里选一个" type="list">
       <formula1>"组头,入组,虚设,Side,幕僚"</formula1>
     </dataValidation>
@@ -6530,6 +6527,9 @@
     <dataValidation sqref="AN2:AN500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="层级编号" error="请填 1～14 的整数（对照「←填写须知」的层级表）" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>14</formula2>
+    </dataValidation>
+    <dataValidation sqref="AH2:AH500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="状态" error="状态只认：管培生 / 试用 / 试用延期 / 产假 / 外包；正式员工留空。确定要填别的吗？" type="list" errorStyle="warning">
+      <formula1>"管培生,试用,试用延期,产假,外包"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
